--- a/contact_forms/027_marketing_consent_form--contact_forms.xlsx
+++ b/contact_forms/027_marketing_consent_form--contact_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -1106,8 +1106,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="34" customWidth="1" min="1" max="1"/>
-    <col width="39" customWidth="1" min="2" max="2"/>
-    <col width="39" customWidth="1" min="3" max="3"/>
+    <col width="18" customWidth="1" min="2" max="2"/>
+    <col width="18" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1135,12 +1135,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'id':_1,_'name':_'ceo'}</t>
+          <t>ceo</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'id': 1, 'name': 'CEO'}</t>
+          <t>CEO</t>
         </is>
       </c>
     </row>
@@ -1152,12 +1152,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'id':_2,_'name':_'cmo'}</t>
+          <t>cmo</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'id': 2, 'name': 'CMO'}</t>
+          <t>CMO</t>
         </is>
       </c>
     </row>
@@ -1169,12 +1169,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'id':_3,_'name':_'customer_service'}</t>
+          <t>customer_service</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'id': 3, 'name': 'Customer Service'}</t>
+          <t>Customer Service</t>
         </is>
       </c>
     </row>
@@ -1186,12 +1186,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'id':_1,_'name':_'personal'}</t>
+          <t>personal</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'id': 1, 'name': 'Personal'}</t>
+          <t>Personal</t>
         </is>
       </c>
     </row>
@@ -1203,12 +1203,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'id':_2,_'name':_'work'}</t>
+          <t>work</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'id': 2, 'name': 'Work'}</t>
+          <t>Work</t>
         </is>
       </c>
     </row>
@@ -1220,12 +1220,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'id':_3,_'name':_'other'}</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'id': 3, 'name': 'Other'}</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
@@ -1237,12 +1237,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{'id':_1,_'name':_'never'}</t>
+          <t>never</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{'id': 1, 'name': 'Never'}</t>
+          <t>Never</t>
         </is>
       </c>
     </row>
@@ -1254,12 +1254,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>{'id':_2,_'name':_'occasionally'}</t>
+          <t>occasionally</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>{'id': 2, 'name': 'Occasionally'}</t>
+          <t>Occasionally</t>
         </is>
       </c>
     </row>
@@ -1271,12 +1271,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>{'id':_3,_'name':_'frequently'}</t>
+          <t>frequently</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>{'id': 3, 'name': 'Frequently'}</t>
+          <t>Frequently</t>
         </is>
       </c>
     </row>
@@ -1288,12 +1288,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>{'id':_1,_'name':_'mobile'}</t>
+          <t>mobile</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>{'id': 1, 'name': 'Mobile'}</t>
+          <t>Mobile</t>
         </is>
       </c>
     </row>
@@ -1305,12 +1305,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>{'id':_2,_'name':_'landline'}</t>
+          <t>landline</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>{'id': 2, 'name': 'Landline'}</t>
+          <t>Landline</t>
         </is>
       </c>
     </row>
@@ -1322,12 +1322,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>{'id':_3,_'name':_'other'}</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>{'id': 3, 'name': 'Other'}</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
@@ -1339,12 +1339,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>{'id':_1,_'name':_'never'}</t>
+          <t>never</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>{'id': 1, 'name': 'Never'}</t>
+          <t>Never</t>
         </is>
       </c>
     </row>
@@ -1356,12 +1356,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>{'id':_2,_'name':_'occasionally'}</t>
+          <t>occasionally</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>{'id': 2, 'name': 'Occasionally'}</t>
+          <t>Occasionally</t>
         </is>
       </c>
     </row>
@@ -1373,12 +1373,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>{'id':_3,_'name':_'frequently'}</t>
+          <t>frequently</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>{'id': 3, 'name': 'Frequently'}</t>
+          <t>Frequently</t>
         </is>
       </c>
     </row>
@@ -1390,12 +1390,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>{'id':_1,_'name':_'email'}</t>
+          <t>email</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>{'id': 1, 'name': 'Email'}</t>
+          <t>Email</t>
         </is>
       </c>
     </row>
@@ -1407,12 +1407,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>{'id':_2,_'name':_'phone'}</t>
+          <t>phone</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>{'id': 2, 'name': 'Phone'}</t>
+          <t>Phone</t>
         </is>
       </c>
     </row>
@@ -1424,12 +1424,12 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>{'id':_3,_'name':_'other'}</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>{'id': 3, 'name': 'Other'}</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
@@ -1441,12 +1441,12 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>{'id':_1,_'name':_'phone'}</t>
+          <t>phone</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>{'id': 1, 'name': 'Phone'}</t>
+          <t>Phone</t>
         </is>
       </c>
     </row>
@@ -1458,12 +1458,12 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>{'id':_2,_'name':_'email'}</t>
+          <t>email</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>{'id': 2, 'name': 'Email'}</t>
+          <t>Email</t>
         </is>
       </c>
     </row>
@@ -1475,12 +1475,12 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>{'id':_3,_'name':_'in-person'}</t>
+          <t>in-person</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>{'id': 3, 'name': 'In-person'}</t>
+          <t>In-person</t>
         </is>
       </c>
     </row>
@@ -1492,12 +1492,12 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>{'id':_1,_'name':_'local'}</t>
+          <t>local</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>{'id': 1, 'name': 'Local'}</t>
+          <t>Local</t>
         </is>
       </c>
     </row>
@@ -1509,12 +1509,12 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>{'id':_2,_'name':_'utc'}</t>
+          <t>utc</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>{'id': 2, 'name': 'UTC'}</t>
+          <t>UTC</t>
         </is>
       </c>
     </row>
@@ -1526,12 +1526,12 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>{'id':_3,_'name':_'other'}</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>{'id': 3, 'name': 'Other'}</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
@@ -1543,12 +1543,12 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>{'id':_1,_'name':_'morning'}</t>
+          <t>morning</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>{'id': 1, 'name': 'Morning'}</t>
+          <t>Morning</t>
         </is>
       </c>
     </row>
@@ -1560,12 +1560,12 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>{'id':_2,_'name':_'afternoon'}</t>
+          <t>afternoon</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>{'id': 2, 'name': 'Afternoon'}</t>
+          <t>Afternoon</t>
         </is>
       </c>
     </row>
@@ -1577,12 +1577,12 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>{'id':_3,_'name':_'night'}</t>
+          <t>night</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>{'id': 3, 'name': 'Night'}</t>
+          <t>Night</t>
         </is>
       </c>
     </row>
@@ -1594,12 +1594,12 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>{'id':_1,_'name':_'january'}</t>
+          <t>january</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>{'id': 1, 'name': 'January'}</t>
+          <t>January</t>
         </is>
       </c>
     </row>
@@ -1611,12 +1611,12 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>{'id':_2,_'name':_'february'}</t>
+          <t>february</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>{'id': 2, 'name': 'February'}</t>
+          <t>February</t>
         </is>
       </c>
     </row>
@@ -1628,12 +1628,12 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>{'id':_3,_'name':_'march'}</t>
+          <t>march</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>{'id': 3, 'name': 'March'}</t>
+          <t>March</t>
         </is>
       </c>
     </row>
@@ -1645,12 +1645,12 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>{'id':_1,_'name':_'january'}</t>
+          <t>january</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>{'id': 1, 'name': 'January'}</t>
+          <t>January</t>
         </is>
       </c>
     </row>
@@ -1662,12 +1662,12 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>{'id':_2,_'name':_'february'}</t>
+          <t>february</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>{'id': 2, 'name': 'February'}</t>
+          <t>February</t>
         </is>
       </c>
     </row>
@@ -1679,12 +1679,12 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>{'id':_3,_'name':_'march'}</t>
+          <t>march</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>{'id': 3, 'name': 'March'}</t>
+          <t>March</t>
         </is>
       </c>
     </row>
@@ -1696,12 +1696,12 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>{'id':_1,_'name':_'first'}</t>
+          <t>first</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>{'id': 1, 'name': 'First'}</t>
+          <t>First</t>
         </is>
       </c>
     </row>
@@ -1713,12 +1713,12 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>{'id':_2,_'name':_'second'}</t>
+          <t>second</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>{'id': 2, 'name': 'Second'}</t>
+          <t>Second</t>
         </is>
       </c>
     </row>
@@ -1730,12 +1730,12 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>{'id':_3,_'name':_'last'}</t>
+          <t>last</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>{'id': 3, 'name': 'Last'}</t>
+          <t>Last</t>
         </is>
       </c>
     </row>
@@ -1747,12 +1747,12 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>{'id':_1,_'name':_'first'}</t>
+          <t>first</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>{'id': 1, 'name': 'First'}</t>
+          <t>First</t>
         </is>
       </c>
     </row>
@@ -1764,12 +1764,12 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>{'id':_2,_'name':_'second'}</t>
+          <t>second</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>{'id': 2, 'name': 'Second'}</t>
+          <t>Second</t>
         </is>
       </c>
     </row>
@@ -1781,12 +1781,12 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>{'id':_3,_'name':_'last'}</t>
+          <t>last</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>{'id': 3, 'name': 'Last'}</t>
+          <t>Last</t>
         </is>
       </c>
     </row>
@@ -1798,12 +1798,12 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>{'id':_1,_'name':_'monday'}</t>
+          <t>monday</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>{'id': 1, 'name': 'Monday'}</t>
+          <t>Monday</t>
         </is>
       </c>
     </row>
@@ -1815,12 +1815,12 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>{'id':_2,_'name':_'tuesday'}</t>
+          <t>tuesday</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>{'id': 2, 'name': 'Tuesday'}</t>
+          <t>Tuesday</t>
         </is>
       </c>
     </row>
@@ -1832,12 +1832,12 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>{'id':_3,_'name':_'wednesday'}</t>
+          <t>wednesday</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>{'id': 3, 'name': 'Wednesday'}</t>
+          <t>Wednesday</t>
         </is>
       </c>
     </row>
